--- a/Employee_Reports_wi52/Lemuel Carcellar Macatangay Q0550.xlsx
+++ b/Employee_Reports_wi52/Lemuel Carcellar Macatangay Q0550.xlsx
@@ -566,11 +566,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>-517</v>
+        <v>-525</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -615,11 +615,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>-182</v>
+        <v>-190</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>19-Aug-2026</t>
+          <t>27-Aug-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
